--- a/reports/pdf_rolling5_20260717.xlsx
+++ b/reports/pdf_rolling5_20260717.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      오늘 2026-07-17  vs  5일전 2026-07-10      매수 16종목  /  매도 18종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 186억(3.7%)      오늘 2026-07-17  vs  5일전 2026-07-10      매수 16종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -664,10 +664,8 @@
       <c r="B6" s="11" t="n">
         <v>263</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="11" t="n">
+        <v>4093458240</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -687,10 +685,8 @@
       <c r="H6" s="15" t="n">
         <v>-78</v>
       </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="15" t="n">
+        <v>-3245923200</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -712,10 +708,8 @@
       <c r="B7" s="11" t="n">
         <v>242</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="11" t="n">
+        <v>10562816000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,10 +729,8 @@
       <c r="H7" s="15" t="n">
         <v>-69</v>
       </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="15" t="n">
+        <v>-923363520</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -760,10 +752,8 @@
       <c r="B8" s="11" t="n">
         <v>207</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="11" t="n">
+        <v>2082188160</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -783,10 +773,8 @@
       <c r="H8" s="15" t="n">
         <v>-61</v>
       </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="15" t="n">
+        <v>-1857718400</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -808,10 +796,8 @@
       <c r="B9" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C9" s="11" t="n">
+        <v>1047552000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -831,10 +817,8 @@
       <c r="H9" s="15" t="n">
         <v>-54</v>
       </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="15" t="n">
+        <v>-801377280</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -856,10 +840,8 @@
       <c r="B10" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C10" s="11" t="n">
+        <v>5548256000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -879,10 +861,8 @@
       <c r="H10" s="15" t="n">
         <v>-39</v>
       </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="15" t="n">
+        <v>-1849286400</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -904,10 +884,8 @@
       <c r="B11" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="11" t="n">
+        <v>1118470080</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -927,10 +905,8 @@
       <c r="H11" s="15" t="n">
         <v>-32</v>
       </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="15" t="n">
+        <v>-817408000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -952,10 +928,8 @@
       <c r="B12" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="11" t="n">
+        <v>4028710400</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -975,10 +949,8 @@
       <c r="H12" s="15" t="n">
         <v>-30</v>
       </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="15" t="n">
+        <v>-785664000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -1000,10 +972,8 @@
       <c r="B13" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C13" s="11" t="n">
+        <v>951129600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -1023,10 +993,8 @@
       <c r="H13" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="15" t="n">
+        <v>-1793932800</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1048,10 +1016,8 @@
       <c r="B14" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="11" t="n">
+        <v>722126400</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1071,10 +1037,8 @@
       <c r="H14" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="15" t="n">
+        <v>-1343168000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1096,10 +1060,8 @@
       <c r="B15" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="11" t="n">
+        <v>445804800</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1119,10 +1081,8 @@
       <c r="H15" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="15" t="n">
+        <v>-3608896000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1144,10 +1104,8 @@
       <c r="B16" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="11" t="n">
+        <v>980294400</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1167,10 +1125,8 @@
       <c r="H16" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="15" t="n">
+        <v>-433008000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1192,10 +1148,8 @@
       <c r="B17" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C17" s="11" t="n">
+        <v>952816000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1215,10 +1169,8 @@
       <c r="H17" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="15" t="n">
+        <v>-428147200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1234,25 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C18" s="11" t="n">
+        <v>461032000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.91%</t>
+          <t>0.62%→0.70%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>149→160</t>
+          <t>70→81</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1263,10 +1213,8 @@
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="15" t="n">
+        <v>-1844128000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1282,25 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C19" s="11" t="n">
+        <v>972259200</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.62%→0.70%</t>
+          <t>2.66%→2.91%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>70→81</t>
+          <t>149→160</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1311,10 +1257,8 @@
       <c r="H19" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="15" t="n">
+        <v>-430528000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1336,10 +1280,8 @@
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="11" t="n">
+        <v>391840000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1359,10 +1301,8 @@
       <c r="H20" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="15" t="n">
+        <v>-374976000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1384,10 +1324,8 @@
       <c r="B21" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C21" s="11" t="n">
+        <v>497289600</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1407,10 +1345,8 @@
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="15" t="n">
+        <v>-990908800</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1437,10 +1373,8 @@
       <c r="H22" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="15" t="n">
+        <v>-230640000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1467,10 +1401,8 @@
       <c r="H23" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="15" t="n">
+        <v>-390451200</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1486,7 +1418,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      오늘 2026-07-17  vs  5일전 2026-07-10      매수 3종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 34억(0.8%)      오늘 2026-07-17  vs  5일전 2026-07-10      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1581,10 +1513,8 @@
       <c r="B28" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C28" s="11" t="n">
+        <v>586673880</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1604,10 +1534,8 @@
       <c r="H28" s="15" t="n">
         <v>-49</v>
       </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="15" t="n">
+        <v>-884697450</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1629,10 +1557,8 @@
       <c r="B29" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C29" s="11" t="n">
+        <v>1265390100</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1652,10 +1578,8 @@
       <c r="H29" s="15" t="n">
         <v>-21</v>
       </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="15" t="n">
+        <v>-401495850</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1677,10 +1601,8 @@
       <c r="B30" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C30" s="11" t="n">
+        <v>1023021000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1700,10 +1622,8 @@
       <c r="H30" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="15" t="n">
+        <v>-861678000</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1753,7 +1673,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      오늘 2026-07-17  vs  5일전 2026-07-10      매수 9종목  /  매도 12종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 359억   ·   현금 6억(100.0%)      오늘 2026-07-17  vs  5일전 2026-07-10      매수 9종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1848,14 +1768,12 @@
       <c r="B39" s="11" t="n">
         <v>198</v>
       </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="11" t="n">
+        <v>136827900</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.44%→6.88%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1871,14 +1789,12 @@
       <c r="H39" s="15" t="n">
         <v>-174</v>
       </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="15" t="n">
+        <v>-42225450</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.43%→0.31%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1896,14 +1812,12 @@
       <c r="B40" s="11" t="n">
         <v>96</v>
       </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C40" s="11" t="n">
+        <v>320688000</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.29%→7.28%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1919,14 +1833,12 @@
       <c r="H40" s="15" t="n">
         <v>-29</v>
       </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="15" t="n">
+        <v>-19448850</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.36%→0.31%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1944,14 +1856,12 @@
       <c r="B41" s="11" t="n">
         <v>77</v>
       </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C41" s="11" t="n">
+        <v>138754000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.41%→2.84%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1961,25 +1871,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-25</v>
       </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="15" t="n">
+        <v>-50468750</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.57%→0.42%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>88→63</t>
+          <t>95→70</t>
         </is>
       </c>
     </row>
@@ -1992,14 +1900,12 @@
       <c r="B42" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C42" s="11" t="n">
+        <v>191568750</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.29%→5.88%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -2009,25 +1915,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-25</v>
       </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" s="15" t="n">
+        <v>-37888750</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.40%→0.28%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>95→70</t>
+          <t>88→63</t>
         </is>
       </c>
     </row>
@@ -2040,14 +1944,12 @@
       <c r="B43" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C43" s="11" t="n">
+        <v>125647000</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.36%→2.74%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -2063,14 +1965,12 @@
       <c r="H43" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="15" t="n">
+        <v>-33753500</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.39%→0.29%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -2088,14 +1988,12 @@
       <c r="B44" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C44" s="11" t="n">
+        <v>36018750</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.59%→0.70%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -2111,14 +2009,12 @@
       <c r="H44" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I44" s="15" t="n">
+        <v>-202521000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.46%→3.87%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -2136,14 +2032,12 @@
       <c r="B45" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C45" s="11" t="n">
+        <v>30642500</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.63%→0.72%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -2159,14 +2053,12 @@
       <c r="H45" s="15" t="n">
         <v>-21</v>
       </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="15" t="n">
+        <v>-346825500</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.32%→3.30%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -2184,14 +2076,12 @@
       <c r="B46" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C46" s="11" t="n">
+        <v>35904000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.87%→0.98%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -2207,14 +2097,12 @@
       <c r="H46" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="15" t="n">
+        <v>-158457000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.62%→3.16%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2232,14 +2120,12 @@
       <c r="B47" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C47" s="11" t="n">
+        <v>36040000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.11%→0.22%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2255,14 +2141,12 @@
       <c r="H47" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="15" t="n">
+        <v>-143514000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.44%→3.03%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2285,14 +2169,12 @@
       <c r="H48" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="15" t="n">
+        <v>-86275000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.76%→1.51%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2315,14 +2197,12 @@
       <c r="H49" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="15" t="n">
+        <v>-83045000</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.55%→3.32%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2345,14 +2225,12 @@
       <c r="H50" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="15" t="n">
+        <v>-54825000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.55%→2.40%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2364,7 +2242,7 @@
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      오늘 2026-07-17  vs  5일전 2026-07-10      매수 1종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 27억(4.7%)      오늘 2026-07-17  vs  5일전 2026-07-10      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B52" s="4" t="n"/>
@@ -2459,10 +2337,8 @@
       <c r="B55" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C55" s="11" t="n">
+        <v>529461120</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260717.xlsx
+++ b/reports/pdf_rolling5_20260717.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>461032000</v>
+        <v>972259200</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.62%→0.70%</t>
+          <t>2.66%→2.91%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>70→81</t>
+          <t>149→160</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>972259200</v>
+        <v>461032000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.91%</t>
+          <t>0.62%→0.70%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>149→160</t>
+          <t>70→81</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1871,23 +1871,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-50468750</v>
+        <v>-37888750</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.57%→0.42%</t>
+          <t>0.40%→0.28%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>95→70</t>
+          <t>88→63</t>
         </is>
       </c>
     </row>
@@ -1915,23 +1915,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-37888750</v>
+        <v>-50468750</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.28%</t>
+          <t>0.57%→0.42%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>88→63</t>
+          <t>95→70</t>
         </is>
       </c>
     </row>
@@ -1959,23 +1959,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>오로스테크놀로지</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-33753500</v>
+        <v>-202521000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.29%</t>
+          <t>4.46%→3.87%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>85→63</t>
+          <t>163→141</t>
         </is>
       </c>
     </row>
@@ -2003,23 +2003,23 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>오로스테크놀로지</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-202521000</v>
+        <v>-33753500</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.87%</t>
+          <t>0.39%→0.29%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>163→141</t>
+          <t>85→63</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260717.xlsx
+++ b/reports/pdf_rolling5_20260717.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>972259200</v>
+        <v>461032000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.91%</t>
+          <t>0.62%→0.70%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>149→160</t>
+          <t>70→81</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>461032000</v>
+        <v>972259200</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.62%→0.70%</t>
+          <t>2.66%→2.91%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>70→81</t>
+          <t>149→160</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1871,23 +1871,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-37888750</v>
+        <v>-50468750</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.28%</t>
+          <t>0.57%→0.42%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>88→63</t>
+          <t>95→70</t>
         </is>
       </c>
     </row>
@@ -1915,23 +1915,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-50468750</v>
+        <v>-37888750</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.57%→0.42%</t>
+          <t>0.40%→0.28%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>95→70</t>
+          <t>88→63</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260717.xlsx
+++ b/reports/pdf_rolling5_20260717.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>461032000</v>
+        <v>972259200</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.62%→0.70%</t>
+          <t>2.66%→2.91%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>70→81</t>
+          <t>149→160</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>972259200</v>
+        <v>461032000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.91%</t>
+          <t>0.62%→0.70%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>149→160</t>
+          <t>70→81</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260717.xlsx
+++ b/reports/pdf_rolling5_20260717.xlsx
@@ -1959,23 +1959,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>오로스테크놀로지</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-202521000</v>
+        <v>-33753500</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.87%</t>
+          <t>0.39%→0.29%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>163→141</t>
+          <t>85→63</t>
         </is>
       </c>
     </row>
@@ -2003,23 +2003,23 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>오로스테크놀로지</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-33753500</v>
+        <v>-202521000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.29%</t>
+          <t>4.46%→3.87%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>85→63</t>
+          <t>163→141</t>
         </is>
       </c>
     </row>
